--- a/Pruebas calificadas/COLEGIO-BELLAVISTA-(IED)-302_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-BELLAVISTA-(IED)-302_Ajustado_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -950,11 +946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -1153,11 +1145,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -1356,11 +1344,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -1559,11 +1543,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -1762,11 +1742,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -1965,11 +1941,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -2168,11 +2140,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -2371,11 +2339,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -2574,11 +2538,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -2777,11 +2737,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -2976,11 +2932,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -3179,11 +3131,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -3382,11 +3330,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -3585,11 +3529,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -3788,11 +3728,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -3991,11 +3927,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -4194,11 +4126,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -4397,11 +4325,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -4600,11 +4524,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -4803,11 +4723,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -5006,11 +4922,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -5209,11 +5121,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -5412,11 +5320,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -5615,11 +5519,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -5818,11 +5718,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -6021,11 +5917,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -6224,11 +6116,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -6427,11 +6315,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -6630,11 +6514,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -6833,11 +6713,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -7036,11 +6912,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -7239,11 +7111,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -7442,11 +7310,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -7645,11 +7509,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -7848,11 +7708,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -8051,11 +7907,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -8254,11 +8106,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -8457,11 +8305,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -8660,11 +8504,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -8863,11 +8703,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -9066,11 +8902,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -9249,11 +9081,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -9452,11 +9280,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -9651,11 +9475,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -9850,11 +9670,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -10053,11 +9869,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -10256,11 +10068,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -10459,11 +10267,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -10662,11 +10466,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -10865,11 +10665,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -11068,11 +10864,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -11267,11 +11059,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -11470,11 +11258,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -11673,11 +11457,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -11876,11 +11656,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -12079,11 +11855,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -12282,11 +12054,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -12485,11 +12253,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -12688,11 +12452,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -12891,11 +12651,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -13094,11 +12850,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -13297,11 +13049,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -13500,11 +13248,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -13703,11 +13447,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
@@ -13906,11 +13646,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001098892</t>
